--- a/Daily_Report/Top 7 broker List with its Turnover 2024-12-29.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-12-29.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="276">
   <si>
     <t>Date: 2024-12-29</t>
   </si>
@@ -62,106 +62,106 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
     <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
-  </si>
-  <si>
     <t>58</t>
   </si>
   <si>
+    <t>34</t>
+  </si>
+  <si>
     <t>45</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>42</t>
   </si>
   <si>
+    <t>57</t>
+  </si>
+  <si>
     <t>49</t>
   </si>
   <si>
     <t>38</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>694,709,821.6</t>
-  </si>
-  <si>
-    <t>436,516,687.29</t>
-  </si>
-  <si>
-    <t>408,739,503.9</t>
-  </si>
-  <si>
-    <t>381,887,301.1</t>
-  </si>
-  <si>
-    <t>306,219,712.89</t>
-  </si>
-  <si>
-    <t>302,186,292.3</t>
-  </si>
-  <si>
-    <t>293,168,922.0</t>
-  </si>
-  <si>
-    <t>407,567,056.5</t>
-  </si>
-  <si>
-    <t>278,241,500.7</t>
-  </si>
-  <si>
-    <t>207,232,893.9</t>
-  </si>
-  <si>
-    <t>199,860,383.6</t>
-  </si>
-  <si>
-    <t>134,433,494.4</t>
-  </si>
-  <si>
-    <t>168,340,500.4</t>
-  </si>
-  <si>
-    <t>167,206,974.4</t>
-  </si>
-  <si>
-    <t>287,142,765.1</t>
-  </si>
-  <si>
-    <t>158,275,186.6</t>
-  </si>
-  <si>
-    <t>201,506,610.0</t>
-  </si>
-  <si>
-    <t>182,026,917.5</t>
-  </si>
-  <si>
-    <t>171,786,218.5</t>
-  </si>
-  <si>
-    <t>133,845,791.9</t>
-  </si>
-  <si>
-    <t>125,961,947.6</t>
+    <t>667,385,868.5</t>
+  </si>
+  <si>
+    <t>516,881,463.6</t>
+  </si>
+  <si>
+    <t>400,924,651.4</t>
+  </si>
+  <si>
+    <t>356,433,029.0</t>
+  </si>
+  <si>
+    <t>309,924,979.7</t>
+  </si>
+  <si>
+    <t>307,941,746.3</t>
+  </si>
+  <si>
+    <t>306,160,498.29</t>
+  </si>
+  <si>
+    <t>400,229,864.1</t>
+  </si>
+  <si>
+    <t>253,057,471.5</t>
+  </si>
+  <si>
+    <t>219,347,310.7</t>
+  </si>
+  <si>
+    <t>177,402,106.0</t>
+  </si>
+  <si>
+    <t>152,763,517.8</t>
+  </si>
+  <si>
+    <t>142,949,666.9</t>
+  </si>
+  <si>
+    <t>160,740,061.19</t>
+  </si>
+  <si>
+    <t>267,156,004.4</t>
+  </si>
+  <si>
+    <t>263,823,992.1</t>
+  </si>
+  <si>
+    <t>181,577,340.7</t>
+  </si>
+  <si>
+    <t>179,030,923.0</t>
+  </si>
+  <si>
+    <t>157,161,461.9</t>
+  </si>
+  <si>
+    <t>164,992,079.4</t>
+  </si>
+  <si>
+    <t>145,420,437.1</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,256 +182,259 @@
     <t>PRVU</t>
   </si>
   <si>
-    <t>85,156,116.5</t>
+    <t>86,512,283.1</t>
   </si>
   <si>
     <t>KBL</t>
   </si>
   <si>
-    <t>29,298,616.7</t>
+    <t>29,123,599.7</t>
+  </si>
+  <si>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>22,062,781.0</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>17,899,593.2</t>
   </si>
   <si>
     <t>GBIME</t>
   </si>
   <si>
-    <t>27,345,287.8</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>21,998,971.0</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>17,434,593.2</t>
+    <t>13,411,150.8</t>
+  </si>
+  <si>
+    <t>RFPL</t>
+  </si>
+  <si>
+    <t>65,342,316.2</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>14,254,517.0</t>
+  </si>
+  <si>
+    <t>EDBL</t>
+  </si>
+  <si>
+    <t>6,585,028.3</t>
+  </si>
+  <si>
+    <t>MMKJL</t>
+  </si>
+  <si>
+    <t>6,090,214.6</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>5,102,300.0</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>19,895,558.0</t>
   </si>
   <si>
     <t>SHLB</t>
   </si>
   <si>
-    <t>56,894,075.0</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>19,895,558.0</t>
+    <t>16,779,821.2</t>
+  </si>
+  <si>
+    <t>8,863,908.1</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>6,918,478.0</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>6,823,308.8</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>6,334,731.0</t>
+  </si>
+  <si>
+    <t>5,443,018.2</t>
+  </si>
+  <si>
+    <t>5,026,154.7</t>
+  </si>
+  <si>
+    <t>4,967,228.59</t>
+  </si>
+  <si>
+    <t>SARBTM</t>
+  </si>
+  <si>
+    <t>4,519,990.0</t>
+  </si>
+  <si>
+    <t>10,276,082.6</t>
+  </si>
+  <si>
+    <t>7,145,645.5</t>
+  </si>
+  <si>
+    <t>VLUCL</t>
+  </si>
+  <si>
+    <t>4,137,517.9</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>3,491,223.0</t>
+  </si>
+  <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>3,453,839.0</t>
+  </si>
+  <si>
+    <t>6,123,807.7</t>
+  </si>
+  <si>
+    <t>5,571,552.0</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>4,420,080.0</t>
+  </si>
+  <si>
+    <t>4,406,776.5</t>
+  </si>
+  <si>
+    <t>4,010,322.5</t>
+  </si>
+  <si>
+    <t>23,327,588.6</t>
+  </si>
+  <si>
+    <t>8,162,036.0</t>
+  </si>
+  <si>
+    <t>USHEC</t>
+  </si>
+  <si>
+    <t>6,840,170.0</t>
+  </si>
+  <si>
+    <t>ULBSL</t>
+  </si>
+  <si>
+    <t>6,181,802.0</t>
+  </si>
+  <si>
+    <t>ANLB</t>
+  </si>
+  <si>
+    <t>5,829,554.5</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>25,118,718.7</t>
   </si>
   <si>
     <t>SAPDBL</t>
   </si>
   <si>
-    <t>13,039,529.3</t>
-  </si>
-  <si>
-    <t>BEDC</t>
-  </si>
-  <si>
-    <t>10,619,090.0</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>10,288,738.1</t>
-  </si>
-  <si>
-    <t>RFPL</t>
-  </si>
-  <si>
-    <t>18,063,273.2</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>14,245,117.0</t>
+    <t>12,481,916.9</t>
+  </si>
+  <si>
+    <t>MLBSL</t>
+  </si>
+  <si>
+    <t>9,921,036.19</t>
+  </si>
+  <si>
+    <t>MKHL</t>
+  </si>
+  <si>
+    <t>7,566,087.5</t>
+  </si>
+  <si>
+    <t>7,323,384.2</t>
+  </si>
+  <si>
+    <t>49,444,671.5</t>
+  </si>
+  <si>
+    <t>16,525,219.8</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>13,814,926.0</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>9,822,076.8</t>
   </si>
   <si>
     <t>JOSHI</t>
   </si>
   <si>
-    <t>8,857,068.19</t>
-  </si>
-  <si>
-    <t>6,978,048.0</t>
-  </si>
-  <si>
-    <t>EDBL</t>
-  </si>
-  <si>
-    <t>6,585,028.3</t>
-  </si>
-  <si>
-    <t>SARBTM</t>
-  </si>
-  <si>
-    <t>16,207,793.0</t>
-  </si>
-  <si>
-    <t>11,616,414.2</t>
-  </si>
-  <si>
-    <t>CBBL</t>
-  </si>
-  <si>
-    <t>9,740,627.0</t>
-  </si>
-  <si>
-    <t>SGHC</t>
-  </si>
-  <si>
-    <t>8,797,725.0</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>7,905,248.0</t>
-  </si>
-  <si>
-    <t>9,398,877.69</t>
-  </si>
-  <si>
-    <t>7,170,646.7</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>4,420,080.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>3,975,867.5</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>3,492,699.5</t>
-  </si>
-  <si>
-    <t>22,593,870.6</t>
-  </si>
-  <si>
-    <t>22,417,535.0</t>
-  </si>
-  <si>
-    <t>NESDO</t>
-  </si>
-  <si>
-    <t>13,770,480.0</t>
-  </si>
-  <si>
-    <t>6,645,707.0</t>
-  </si>
-  <si>
-    <t>USHEC</t>
-  </si>
-  <si>
-    <t>6,073,271.0</t>
-  </si>
-  <si>
-    <t>UNLB</t>
-  </si>
-  <si>
-    <t>13,006,878.0</t>
-  </si>
-  <si>
-    <t>NABBC</t>
-  </si>
-  <si>
-    <t>12,565,760.0</t>
-  </si>
-  <si>
-    <t>12,509,032.1</t>
-  </si>
-  <si>
-    <t>8,996,441.0</t>
-  </si>
-  <si>
-    <t>7,359,290.5</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>33,664,818.4</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>24,906,421.7</t>
-  </si>
-  <si>
-    <t>14,973,201.2</t>
-  </si>
-  <si>
-    <t>11,359,003.9</t>
-  </si>
-  <si>
-    <t>MLBSL</t>
-  </si>
-  <si>
-    <t>9,869,103.19</t>
-  </si>
-  <si>
-    <t>7,621,096.3</t>
-  </si>
-  <si>
-    <t>4,905,340.59</t>
-  </si>
-  <si>
-    <t>4,429,636.7</t>
+    <t>7,719,925.0</t>
+  </si>
+  <si>
+    <t>8,675,826.1</t>
+  </si>
+  <si>
+    <t>5,544,877.1</t>
   </si>
   <si>
     <t>SINDU</t>
   </si>
   <si>
-    <t>3,997,771.3</t>
-  </si>
-  <si>
-    <t>3,939,579.0</t>
-  </si>
-  <si>
-    <t>16,428,024.8</t>
-  </si>
-  <si>
-    <t>12,879,777.8</t>
-  </si>
-  <si>
-    <t>NICA</t>
-  </si>
-  <si>
-    <t>9,519,914.8</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>7,602,893.0</t>
-  </si>
-  <si>
-    <t>7,227,434.0</t>
-  </si>
-  <si>
-    <t>18,809,330.6</t>
-  </si>
-  <si>
-    <t>PPL</t>
-  </si>
-  <si>
-    <t>13,654,177.8</t>
-  </si>
-  <si>
-    <t>11,201,255.9</t>
+    <t>5,443,025.0</t>
+  </si>
+  <si>
+    <t>4,922,240.59</t>
+  </si>
+  <si>
+    <t>GLBSL</t>
+  </si>
+  <si>
+    <t>4,184,813.6</t>
+  </si>
+  <si>
+    <t>11,554,855.9</t>
+  </si>
+  <si>
+    <t>7,635,616.9</t>
+  </si>
+  <si>
+    <t>6,811,712.7</t>
   </si>
   <si>
     <t>NIMB</t>
@@ -440,79 +443,67 @@
     <t>5,802,008.2</t>
   </si>
   <si>
-    <t>5,645,298.7</t>
-  </si>
-  <si>
-    <t>13,379,352.0</t>
-  </si>
-  <si>
-    <t>NLICL</t>
-  </si>
-  <si>
-    <t>12,190,048.0</t>
-  </si>
-  <si>
-    <t>9,544,103.3</t>
-  </si>
-  <si>
-    <t>8,196,428.6</t>
-  </si>
-  <si>
-    <t>4,033,699.1</t>
+    <t>4,559,192.7</t>
+  </si>
+  <si>
+    <t>15,967,436.8</t>
+  </si>
+  <si>
+    <t>DLBS</t>
+  </si>
+  <si>
+    <t>6,115,474.5</t>
+  </si>
+  <si>
+    <t>4,078,649.6</t>
+  </si>
+  <si>
+    <t>3,277,051.8</t>
+  </si>
+  <si>
+    <t>TVCL</t>
+  </si>
+  <si>
+    <t>3,231,300.0</t>
+  </si>
+  <si>
+    <t>8,915,276.2</t>
+  </si>
+  <si>
+    <t>MBL</t>
+  </si>
+  <si>
+    <t>5,839,854.0</t>
+  </si>
+  <si>
+    <t>5,837,475.8</t>
+  </si>
+  <si>
+    <t>4,083,666.0</t>
+  </si>
+  <si>
+    <t>4,064,519.1</t>
+  </si>
+  <si>
+    <t>8,631,891.1</t>
   </si>
   <si>
     <t>CFCL</t>
   </si>
   <si>
-    <t>5,450,287.2</t>
-  </si>
-  <si>
-    <t>USLB</t>
-  </si>
-  <si>
-    <t>4,152,300.0</t>
-  </si>
-  <si>
-    <t>3,818,027.6</t>
+    <t>5,539,868.2</t>
+  </si>
+  <si>
+    <t>4,072,373.0</t>
+  </si>
+  <si>
+    <t>3,836,917.6</t>
   </si>
   <si>
     <t>SPDL</t>
   </si>
   <si>
-    <t>3,332,877.7</t>
-  </si>
-  <si>
-    <t>ANLB</t>
-  </si>
-  <si>
-    <t>3,181,900.0</t>
-  </si>
-  <si>
-    <t>14,095,095.8</t>
-  </si>
-  <si>
-    <t>BFC</t>
-  </si>
-  <si>
-    <t>3,277,051.8</t>
-  </si>
-  <si>
-    <t>MLBBL</t>
-  </si>
-  <si>
-    <t>2,681,840.0</t>
-  </si>
-  <si>
-    <t>BGWT</t>
-  </si>
-  <si>
-    <t>2,401,519.5</t>
-  </si>
-  <si>
-    <t>MKHL</t>
-  </si>
-  <si>
-    <t>2,346,182.0</t>
+    <t>3,336,777.7</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -530,109 +521,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>241,077,583.3</t>
-  </si>
-  <si>
-    <t>233,642,327.7</t>
-  </si>
-  <si>
-    <t>178,253,717.4</t>
-  </si>
-  <si>
-    <t>119,434,098.5</t>
-  </si>
-  <si>
-    <t>119,085,731.6</t>
+    <t>261,082,664.8</t>
+  </si>
+  <si>
+    <t>160,941,667.9</t>
+  </si>
+  <si>
+    <t>153,478,594.9</t>
+  </si>
+  <si>
+    <t>121,322,747.1</t>
+  </si>
+  <si>
+    <t>111,838,618.1</t>
+  </si>
+  <si>
+    <t>Hydro Power</t>
+  </si>
+  <si>
+    <t>1,221,458,307.4</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,197,162,141.72</t>
-  </si>
-  <si>
-    <t>Hydro Power</t>
-  </si>
-  <si>
-    <t>1,087,958,312.3</t>
+    <t>1,155,365,788.52</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>707,539,548.9</t>
+    <t>689,899,143.7</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>667,044,738.5</t>
+    <t>674,677,676.29</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>476,564,498.7</t>
+    <t>513,516,141.3</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>406,510,405.0</t>
+    <t>472,884,094.5</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>295,156,631.7</t>
+    <t>281,665,253.7</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>180,973,638.0</t>
+    <t>193,315,585.2</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>96,965,870.5</t>
+    <t>115,623,506.8</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>49,310,899.5</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>47,828,699.9</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>56,631,615.7</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>54,969,585.3</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>46,621,900.6</t>
+    <t>36,670,538.7</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>9,789,652.1</t>
+    <t>10,245,822.1</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>8,107,321.8</t>
+    <t>8,500,921.8</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>4,620,997.4</t>
+    <t>3,906,385.35</t>
   </si>
   <si>
     <t>Total</t>
@@ -644,214 +635,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>107,045,581.9</t>
-  </si>
-  <si>
-    <t>98,815,159.0</t>
-  </si>
-  <si>
-    <t>67,210,712.3</t>
-  </si>
-  <si>
-    <t>57,100,294.3</t>
-  </si>
-  <si>
-    <t>26,168,293.7</t>
-  </si>
-  <si>
-    <t>80,011,852.9</t>
-  </si>
-  <si>
-    <t>50,198,307.2</t>
-  </si>
-  <si>
-    <t>42,374,555.2</t>
-  </si>
-  <si>
-    <t>33,461,074.2</t>
-  </si>
-  <si>
-    <t>28,732,121.3</t>
-  </si>
-  <si>
-    <t>55,983,623.3</t>
-  </si>
-  <si>
-    <t>38,892,093.6</t>
-  </si>
-  <si>
-    <t>27,526,968.4</t>
-  </si>
-  <si>
-    <t>25,242,998.3</t>
-  </si>
-  <si>
-    <t>18,440,543.2</t>
-  </si>
-  <si>
-    <t>50,190,366.5</t>
-  </si>
-  <si>
-    <t>40,802,936.29</t>
-  </si>
-  <si>
-    <t>37,239,024.79</t>
-  </si>
-  <si>
-    <t>23,515,809.1</t>
-  </si>
-  <si>
-    <t>15,139,456.6</t>
-  </si>
-  <si>
-    <t>31,987,938.3</t>
-  </si>
-  <si>
-    <t>30,552,784.4</t>
-  </si>
-  <si>
-    <t>24,314,833.6</t>
-  </si>
-  <si>
-    <t>17,307,499.1</t>
-  </si>
-  <si>
-    <t>10,469,974.1</t>
-  </si>
-  <si>
-    <t>41,586,302.7</t>
-  </si>
-  <si>
-    <t>31,473,233.3</t>
-  </si>
-  <si>
-    <t>27,403,003.3</t>
-  </si>
-  <si>
-    <t>27,109,078.5</t>
-  </si>
-  <si>
-    <t>21,100,726.39</t>
-  </si>
-  <si>
-    <t>43,178,358.6</t>
-  </si>
-  <si>
-    <t>41,429,341.9</t>
-  </si>
-  <si>
-    <t>26,920,793.9</t>
-  </si>
-  <si>
-    <t>21,591,884.3</t>
-  </si>
-  <si>
-    <t>15,017,316.0</t>
-  </si>
-  <si>
-    <t>58,670,138.5</t>
-  </si>
-  <si>
-    <t>55,196,783.7</t>
-  </si>
-  <si>
-    <t>50,033,092.7</t>
-  </si>
-  <si>
-    <t>36,555,213.4</t>
-  </si>
-  <si>
-    <t>26,065,168.4</t>
-  </si>
-  <si>
-    <t>36,272,555.2</t>
-  </si>
-  <si>
-    <t>35,646,749.2</t>
-  </si>
-  <si>
-    <t>18,904,021.89</t>
-  </si>
-  <si>
-    <t>18,201,521.7</t>
-  </si>
-  <si>
-    <t>16,221,914.2</t>
-  </si>
-  <si>
-    <t>41,785,082.79</t>
-  </si>
-  <si>
-    <t>35,662,566.2</t>
-  </si>
-  <si>
-    <t>33,148,333.7</t>
-  </si>
-  <si>
-    <t>26,913,736.5</t>
-  </si>
-  <si>
-    <t>25,287,381.0</t>
-  </si>
-  <si>
-    <t>59,840,340.6</t>
-  </si>
-  <si>
-    <t>33,870,111.79</t>
-  </si>
-  <si>
-    <t>19,474,673.7</t>
-  </si>
-  <si>
-    <t>18,505,739.3</t>
-  </si>
-  <si>
-    <t>18,331,185.5</t>
-  </si>
-  <si>
-    <t>33,753,766.7</t>
-  </si>
-  <si>
-    <t>31,541,629.4</t>
-  </si>
-  <si>
-    <t>29,329,057.0</t>
-  </si>
-  <si>
-    <t>16,210,960.2</t>
-  </si>
-  <si>
-    <t>15,839,873.0</t>
-  </si>
-  <si>
-    <t>35,898,560.9</t>
-  </si>
-  <si>
-    <t>31,888,011.5</t>
-  </si>
-  <si>
-    <t>20,465,365.2</t>
-  </si>
-  <si>
-    <t>17,044,219.1</t>
-  </si>
-  <si>
-    <t>8,989,310.4</t>
-  </si>
-  <si>
-    <t>32,426,076.9</t>
-  </si>
-  <si>
-    <t>26,620,556.5</t>
-  </si>
-  <si>
-    <t>17,149,881.3</t>
-  </si>
-  <si>
-    <t>16,401,252.1</t>
-  </si>
-  <si>
-    <t>15,984,135.5</t>
+    <t>102,780,410.0</t>
+  </si>
+  <si>
+    <t>94,498,724.2</t>
+  </si>
+  <si>
+    <t>67,338,262.3</t>
+  </si>
+  <si>
+    <t>46,424,945.2</t>
+  </si>
+  <si>
+    <t>27,961,890.7</t>
+  </si>
+  <si>
+    <t>100,117,863.4</t>
+  </si>
+  <si>
+    <t>43,598,453.5</t>
+  </si>
+  <si>
+    <t>25,264,585.9</t>
+  </si>
+  <si>
+    <t>20,739,471.89</t>
+  </si>
+  <si>
+    <t>18,297,370.2</t>
+  </si>
+  <si>
+    <t>51,143,304.6</t>
+  </si>
+  <si>
+    <t>37,530,805.1</t>
+  </si>
+  <si>
+    <t>36,838,051.2</t>
+  </si>
+  <si>
+    <t>36,460,444.2</t>
+  </si>
+  <si>
+    <t>27,261,077.2</t>
+  </si>
+  <si>
+    <t>36,064,546.2</t>
+  </si>
+  <si>
+    <t>35,904,260.6</t>
+  </si>
+  <si>
+    <t>34,962,358.79</t>
+  </si>
+  <si>
+    <t>22,592,790.6</t>
+  </si>
+  <si>
+    <t>16,387,081.5</t>
+  </si>
+  <si>
+    <t>36,231,337.7</t>
+  </si>
+  <si>
+    <t>32,131,708.2</t>
+  </si>
+  <si>
+    <t>28,770,912.1</t>
+  </si>
+  <si>
+    <t>19,386,104.8</t>
+  </si>
+  <si>
+    <t>11,294,197.3</t>
+  </si>
+  <si>
+    <t>32,960,199.2</t>
+  </si>
+  <si>
+    <t>30,392,647.8</t>
+  </si>
+  <si>
+    <t>26,270,933.1</t>
+  </si>
+  <si>
+    <t>18,030,809.1</t>
+  </si>
+  <si>
+    <t>11,501,219.3</t>
+  </si>
+  <si>
+    <t>35,038,164.6</t>
+  </si>
+  <si>
+    <t>29,244,082.0</t>
+  </si>
+  <si>
+    <t>25,588,280.7</t>
+  </si>
+  <si>
+    <t>25,100,607.2</t>
+  </si>
+  <si>
+    <t>18,732,453.39</t>
+  </si>
+  <si>
+    <t>61,249,967.1</t>
+  </si>
+  <si>
+    <t>56,549,348.8</t>
+  </si>
+  <si>
+    <t>41,499,840.9</t>
+  </si>
+  <si>
+    <t>35,428,073.9</t>
+  </si>
+  <si>
+    <t>26,578,427.0</t>
+  </si>
+  <si>
+    <t>91,574,996.4</t>
+  </si>
+  <si>
+    <t>41,526,280.0</t>
+  </si>
+  <si>
+    <t>36,648,714.2</t>
+  </si>
+  <si>
+    <t>25,584,620.0</t>
+  </si>
+  <si>
+    <t>21,397,081.2</t>
+  </si>
+  <si>
+    <t>42,077,422.4</t>
+  </si>
+  <si>
+    <t>38,893,672.4</t>
+  </si>
+  <si>
+    <t>25,668,892.7</t>
+  </si>
+  <si>
+    <t>19,759,169.6</t>
+  </si>
+  <si>
+    <t>18,426,154.2</t>
+  </si>
+  <si>
+    <t>40,280,882.4</t>
+  </si>
+  <si>
+    <t>36,921,341.9</t>
+  </si>
+  <si>
+    <t>27,962,473.2</t>
+  </si>
+  <si>
+    <t>19,652,481.0</t>
+  </si>
+  <si>
+    <t>19,565,725.39</t>
+  </si>
+  <si>
+    <t>40,484,551.5</t>
+  </si>
+  <si>
+    <t>31,951,524.3</t>
+  </si>
+  <si>
+    <t>22,500,259.9</t>
+  </si>
+  <si>
+    <t>21,535,130.8</t>
+  </si>
+  <si>
+    <t>18,667,548.5</t>
+  </si>
+  <si>
+    <t>37,049,296.9</t>
+  </si>
+  <si>
+    <t>30,762,526.8</t>
+  </si>
+  <si>
+    <t>23,954,098.9</t>
+  </si>
+  <si>
+    <t>20,393,869.1</t>
+  </si>
+  <si>
+    <t>18,853,914.1</t>
+  </si>
+  <si>
+    <t>43,958,472.2</t>
+  </si>
+  <si>
+    <t>34,609,598.79</t>
+  </si>
+  <si>
+    <t>21,192,848.7</t>
+  </si>
+  <si>
+    <t>15,694,867.1</t>
+  </si>
+  <si>
+    <t>8,181,680.2</t>
   </si>
 </sst>
 </file>
@@ -1660,7 +1651,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1225779654358063</v>
+        <v>0.1296285809803598</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1669,7 +1660,7 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.130336540744659</v>
+        <v>0.1264164432303314</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>74</v>
@@ -1678,7 +1669,7 @@
         <v>75</v>
       </c>
       <c r="J9" s="14">
-        <v>0.04419262886911773</v>
+        <v>0.04962418232584638</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>83</v>
@@ -1687,34 +1678,34 @@
         <v>84</v>
       </c>
       <c r="M9" s="16">
-        <v>0.04244129865883094</v>
+        <v>0.01777257011723232</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P9" s="18">
-        <v>0.03069324835749332</v>
+        <v>0.03315667749642833</v>
       </c>
       <c r="Q9" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="S9" s="16">
+        <v>0.01988625372681405</v>
+      </c>
+      <c r="T9" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="R9" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="S9" s="16">
-        <v>0.07476801951549011</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>107</v>
-      </c>
       <c r="U9" s="17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="V9" s="18">
-        <v>0.04436649666433606</v>
+        <v>0.07619398560405337</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1726,7 +1717,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.0421738915861615</v>
+        <v>0.0436383224077811</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1735,7 +1726,7 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.04557800097645889</v>
+        <v>0.02757792260670266</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>76</v>
@@ -1744,7 +1735,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="14">
-        <v>0.03485133407483201</v>
+        <v>0.04185280486347266</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>72</v>
@@ -1753,34 +1744,34 @@
         <v>85</v>
       </c>
       <c r="M10" s="16">
-        <v>0.03041843540369036</v>
+        <v>0.0152708019659985</v>
       </c>
       <c r="N10" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="P10" s="18">
+        <v>0.02305604894099473</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="S10" s="16">
+        <v>0.01809287654870976</v>
+      </c>
+      <c r="T10" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="O10" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="P10" s="18">
-        <v>0.02341667240195496</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="R10" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="S10" s="16">
-        <v>0.07418448675939494</v>
-      </c>
-      <c r="T10" s="17" t="s">
-        <v>109</v>
-      </c>
       <c r="U10" s="17" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="V10" s="18">
-        <v>0.04286184195199244</v>
+        <v>0.02665933732575193</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1792,7 +1783,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03936217244924006</v>
+        <v>0.03305850789077654</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1801,52 +1792,52 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.02987177736698636</v>
+        <v>0.01273991962129245</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="J11" s="14">
-        <v>0.02166922481309005</v>
+        <v>0.02210866323397145</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>87</v>
-      </c>
       <c r="M11" s="16">
-        <v>0.0255065485863049</v>
+        <v>0.01410125967871513</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01443434179380684</v>
+        <v>0.01335006266356787</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S11" s="16">
-        <v>0.04556950580117363</v>
+        <v>0.0143536238691519</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="V11" s="18">
-        <v>0.04266834292892751</v>
+        <v>0.02234177837435275</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1858,7 +1849,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03166641713706268</v>
+        <v>0.02682045581850674</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>70</v>
@@ -1867,52 +1858,52 @@
         <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.02432688213062961</v>
+        <v>0.01178261367235457</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>80</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01707211545108498</v>
+        <v>0.01725630483394117</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02303749031365735</v>
+        <v>0.01393593801880801</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01298370853511436</v>
+        <v>0.01126473575437327</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>96</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02199208623732798</v>
+        <v>0.01431042251642904</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03068688501709605</v>
+        <v>0.02019137685731942</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1924,7 +1915,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.0250962238591158</v>
+        <v>0.02009504760737978</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>72</v>
@@ -1933,7 +1924,7 @@
         <v>73</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02357009113131332</v>
+        <v>0.009871315493620653</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>81</v>
@@ -1942,43 +1933,43 @@
         <v>82</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01611057467450236</v>
+        <v>0.01701893055508933</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02070047361415129</v>
+        <v>0.01268117607585688</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01140586106270887</v>
+        <v>0.01114411301516655</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02009777132435468</v>
+        <v>0.01302299070582364</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02510256015472199</v>
+        <v>0.01904084469541119</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1989,7 +1980,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1998,7 +1989,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2007,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2016,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2025,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2034,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2043,7 +2034,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2052,339 +2043,339 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D16" s="10">
-        <v>0.04845882029199743</v>
+        <v>0.03763747463885655</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>122</v>
       </c>
       <c r="G16" s="12">
-        <v>0.01745888879332197</v>
+        <v>0.09565959505613812</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>54</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J16" s="14">
-        <v>0.04019191843032426</v>
+        <v>0.02163954266644528</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M16" s="16">
-        <v>0.04925361630465591</v>
+        <v>0.03241802796002949</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P16" s="18">
-        <v>0.04369200099266372</v>
+        <v>0.05152032861454438</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>148</v>
+        <v>54</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="S16" s="16">
-        <v>0.01803618277492595</v>
+        <v>0.02895117764031463</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V16" s="18">
-        <v>0.04807841057586588</v>
+        <v>0.02819400656822096</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="D17" s="10">
-        <v>0.03585154682661248</v>
+        <v>0.01870269882707293</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>123</v>
       </c>
       <c r="G17" s="12">
-        <v>0.01123746409407886</v>
+        <v>0.03197100488940807</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J17" s="14">
-        <v>0.03151096891077868</v>
+        <v>0.01383022241370714</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M17" s="16">
-        <v>0.0357544693438878</v>
+        <v>0.02142230455303849</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P17" s="18">
-        <v>0.03980817526264489</v>
+        <v>0.01973211228704325</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="S17" s="16">
-        <v>0.01374086153410871</v>
+        <v>0.01896415172729051</v>
       </c>
       <c r="T17" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="U17" s="17" t="s">
-        <v>159</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.01117803271112072</v>
+        <v>0.01809465372169471</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>118</v>
       </c>
       <c r="D18" s="10">
-        <v>0.02155317333144207</v>
+        <v>0.0148655173390145</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01014769155195135</v>
+        <v>0.02672745488642824</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J18" s="14">
-        <v>0.02329090951367669</v>
+        <v>0.01357617941673915</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02933131284474649</v>
+        <v>0.01911077859173371</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P18" s="18">
-        <v>0.0311675013003384</v>
+        <v>0.01316011895507111</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S18" s="16">
-        <v>0.01263468164270534</v>
+        <v>0.01895642883804741</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="V18" s="18">
-        <v>0.009147763622775813</v>
+        <v>0.013301431839223</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01635071730213753</v>
+        <v>0.01133690097005702</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G19" s="12">
-        <v>0.009158347014698424</v>
+        <v>0.01900257117287733</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01860082748904075</v>
+        <v>0.01227722112574493</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01519298542603463</v>
+        <v>0.01627797574281479</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02676649560662559</v>
+        <v>0.01057369368281352</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="R19" s="15" t="s">
         <v>154</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01102921537119637</v>
+        <v>0.01326116399957559</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="V19" s="18">
-        <v>0.00819158962558794</v>
+        <v>0.01253237312228401</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>121</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01420607985254947</v>
+        <v>0.01097323834030208</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G20" s="12">
-        <v>0.009025036418120917</v>
+        <v>0.01493558106385148</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01768224977287301</v>
+        <v>0.01043790544030389</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01478263006844979</v>
+        <v>0.01279116223541674</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01317256508994657</v>
+        <v>0.01042607150649109</v>
       </c>
       <c r="Q20" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="R20" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="R20" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="S20" s="16">
-        <v>0.01052959740755256</v>
+        <v>0.0131989869799605</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="V20" s="18">
-        <v>0.008002833260750606</v>
+        <v>0.01089878582811283</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2392,7 +2383,7 @@
         <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2400,218 +2391,218 @@
         <v>72</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2186649932914498</v>
+        <v>0.2231027554961518</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D32" s="22">
-        <v>0.198718610261648</v>
+        <v>0.2110307731857637</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1292340655638937</v>
+        <v>0.126011996513853</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1218375758689117</v>
+        <v>0.1232317531776204</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D35" s="22">
-        <v>0.08704583053508506</v>
+        <v>0.09379515078140377</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D36" s="22">
-        <v>0.0742502555706607</v>
+        <v>0.08637359447644512</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D37" s="22">
-        <v>0.05391117931434098</v>
+        <v>0.05144694161666043</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D38" s="22">
-        <v>0.03305533808673909</v>
+        <v>0.0353096290533863</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01771108581158357</v>
+        <v>0.02111895494993794</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01034392204328556</v>
+        <v>0.009006772877791811</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01004034757028724</v>
+        <v>0.008736045000342448</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D42" s="22">
-        <v>0.008515619753299893</v>
+        <v>0.006697975837515903</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D43" s="22">
-        <v>0.001788107171261349</v>
+        <v>0.001871427889912248</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001480824865094385</v>
+        <v>0.001552716999300918</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0008440380214655481</v>
+        <v>0.0007135121439142126</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2990,331 +2981,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1540867547452564</v>
+        <v>0.1540044745493439</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1832962066007139</v>
+        <v>0.1936959834130914</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1369665098817966</v>
+        <v>0.1275633823498038</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1314271680556806</v>
+        <v>0.1011818301496408</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1044607415932301</v>
+        <v>0.1169035736811891</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1376180977087954</v>
+        <v>0.1070338776603866</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1472815000493129</v>
+        <v>0.114443779633736</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1422394731262282</v>
+        <v>0.1415953328655175</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1149974529278437</v>
+        <v>0.08434903661729996</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J10" s="14">
-        <v>0.09515129618965124</v>
+        <v>0.09361061977342909</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1068454912809877</v>
+        <v>0.1007321366954464</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="P10" s="18">
-        <v>0.09977406127990658</v>
+        <v>0.1036757612474565</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1041517570517543</v>
+        <v>0.09869609484642973</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1413155992707849</v>
+        <v>0.09551879541084482</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D11" s="10">
-        <v>0.09674645472149172</v>
+        <v>0.1008985438234523</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G11" s="12">
-        <v>0.09707430765614171</v>
+        <v>0.04887887780698506</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06734599454506017</v>
+        <v>0.0918827292643747</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="M11" s="16">
-        <v>0.09751312675947997</v>
+        <v>0.09808955948355728</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P11" s="18">
-        <v>0.07940322773387332</v>
+        <v>0.09283185927074854</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="S11" s="16">
-        <v>0.09068248295258627</v>
+        <v>0.08531137273738322</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="V11" s="18">
-        <v>0.09182690210253595</v>
+        <v>0.0835779953393158</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D12" s="10">
-        <v>0.08219301429838889</v>
+        <v>0.06956237371993441</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G12" s="12">
-        <v>0.07665474235811649</v>
+        <v>0.04012423226701295</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J12" s="14">
-        <v>0.06175815662333391</v>
+        <v>0.09094088894928951</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="M12" s="16">
-        <v>0.06157787659412695</v>
+        <v>0.06338579413750121</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P12" s="18">
-        <v>0.05651987240172219</v>
+        <v>0.06255095932817446</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="S12" s="16">
-        <v>0.08970982202292303</v>
+        <v>0.05855266236762262</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="V12" s="18">
-        <v>0.07364997678710297</v>
+        <v>0.081985126557393</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D13" s="10">
-        <v>0.03766794838128426</v>
+        <v>0.04189763676424024</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G13" s="12">
-        <v>0.06582135834878999</v>
+        <v>0.03539954803672321</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="J13" s="14">
-        <v>0.04511563728009897</v>
+        <v>0.06799551263512055</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03964378117939989</v>
+        <v>0.04597520478384173</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P13" s="18">
-        <v>0.03419105191121091</v>
+        <v>0.03644171344604915</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="S13" s="16">
-        <v>0.06982688142270839</v>
+        <v>0.03734868506199674</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="V13" s="18">
-        <v>0.05122410621682472</v>
+        <v>0.06118507614148341</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3325,7 +3316,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3334,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3343,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3352,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3361,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3370,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3379,7 +3370,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3388,331 +3379,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D16" s="10">
-        <v>0.08445272641298728</v>
+        <v>0.09177594251083547</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G16" s="12">
-        <v>0.08309546062112252</v>
+        <v>0.1771682732868659</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1022291273569264</v>
+        <v>0.1049509483965844</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="M16" s="16">
-        <v>0.15669633535243</v>
+        <v>0.1130110823708203</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1102272821705072</v>
+        <v>0.1306269392650701</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1187961261471158</v>
+        <v>0.1203126803856798</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1106054375709032</v>
+        <v>0.1435798296778511</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D17" s="10">
-        <v>0.07945300610962314</v>
+        <v>0.0847326134236239</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G17" s="12">
-        <v>0.08166182470706203</v>
+        <v>0.08034004491237863</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J17" s="14">
-        <v>0.08725010883392621</v>
+        <v>0.09700993008084212</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M17" s="16">
-        <v>0.08869138015964259</v>
+        <v>0.1035856357184003</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1030032622697296</v>
+        <v>0.1030943821660594</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1055243481009479</v>
+        <v>0.09989722786734745</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="V17" s="18">
-        <v>0.09080279150461931</v>
+        <v>0.1130439720087169</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D18" s="10">
-        <v>0.07202013149140139</v>
+        <v>0.06218267850542598</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G18" s="12">
-        <v>0.0433065274478454</v>
+        <v>0.0709035180808136</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J18" s="14">
-        <v>0.08109892335757665</v>
+        <v>0.06402423151174685</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M18" s="16">
-        <v>0.05099586617283305</v>
+        <v>0.0784508474942708</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P18" s="18">
-        <v>0.09577782149373834</v>
+        <v>0.07259905258937085</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="S18" s="16">
-        <v>0.06772433337142474</v>
+        <v>0.07778776079506826</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="V18" s="18">
-        <v>0.05849829232581481</v>
+        <v>0.06922136858829382</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D19" s="10">
-        <v>0.05261939915547611</v>
+        <v>0.05308484277563033</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G19" s="12">
-        <v>0.04169719561600824</v>
+        <v>0.04949804123716693</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J19" s="14">
-        <v>0.06584569449050506</v>
+        <v>0.04928399770630817</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="M19" s="16">
-        <v>0.0484586401451305</v>
+        <v>0.05513653169330724</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P19" s="18">
-        <v>0.05293898308007982</v>
+        <v>0.06948497930320263</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="S19" s="16">
-        <v>0.05640301871495579</v>
+        <v>0.06622638646769277</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="V19" s="18">
-        <v>0.05594471606373066</v>
+        <v>0.0512635274215583</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D20" s="10">
-        <v>0.03751950467602256</v>
+        <v>0.03982467752836454</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G20" s="12">
-        <v>0.03716218571239029</v>
+        <v>0.04139649553491938</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="J20" s="14">
-        <v>0.06186674094067178</v>
+        <v>0.04595914503051184</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M20" s="16">
-        <v>0.04800155817488114</v>
+        <v>0.05489313225234242</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P20" s="18">
-        <v>0.05172714992771454</v>
+        <v>0.06023247470426469</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02974757832852235</v>
+        <v>0.06122558674338466</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="V20" s="18">
-        <v>0.05452193019285994</v>
+        <v>0.02672350040397097</v>
       </c>
     </row>
   </sheetData>
